--- a/simulacaoes_/lote_eixos_1p5/simulacao_C_11/pre_sizing_results_optimized.xlsx
+++ b/simulacaoes_/lote_eixos_1p5/simulacao_C_11/pre_sizing_results_optimized.xlsx
@@ -497,2052 +497,2052 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>99.99999999341556</v>
+        <v>60.12895816616369</v>
       </c>
       <c r="B2" t="n">
-        <v>77.97872709047142</v>
+        <v>54.31680724392184</v>
       </c>
       <c r="C2" t="n">
-        <v>47.68229516610398</v>
+        <v>45.50845183236608</v>
       </c>
       <c r="D2" t="n">
-        <v>8.719624951249912</v>
+        <v>8.065365997005481</v>
       </c>
       <c r="E2" t="n">
-        <v>2.369824780599562</v>
+        <v>4.233200320833652</v>
       </c>
       <c r="F2" t="n">
-        <v>13.51865069906909</v>
+        <v>7.330891380711732</v>
       </c>
       <c r="G2" t="n">
-        <v>0.02645657438502493</v>
+        <v>0.1584657101904744</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.7995267641600278</v>
+        <v>-0.0004839325493377498</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.9064462558629173</v>
+        <v>-0.6121444124867106</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.9465557647084614</v>
+        <v>-0.5517558592259413</v>
       </c>
       <c r="K2" t="n">
-        <v>-4.942874696406419e-07</v>
+        <v>-0.006026175317353261</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.6220069729448496</v>
+        <v>-0.3072610744996002</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.02475400367729133</v>
+        <v>-0.001878184970241781</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>57.55909872872024</v>
+        <v>99.99999999972623</v>
       </c>
       <c r="B3" t="n">
-        <v>62.19281260660543</v>
+        <v>53.00164470289486</v>
       </c>
       <c r="C3" t="n">
-        <v>47.69253028991933</v>
+        <v>45.50754110772444</v>
       </c>
       <c r="D3" t="n">
-        <v>8.256063745951991</v>
+        <v>9.884643785585967</v>
       </c>
       <c r="E3" t="n">
-        <v>2.014534985465771</v>
+        <v>4.045260816476301</v>
       </c>
       <c r="F3" t="n">
-        <v>6.933241039211455</v>
+        <v>13.80518870123217</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1908845395863809</v>
+        <v>0.02602900753417861</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.004019034740834074</v>
+        <v>-0.7710854941600738</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.6129100820744331</v>
+        <v>-0.8935900797217979</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.5528951016051517</v>
+        <v>-0.936364307328015</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.0008702578513717618</v>
+        <v>-0.0001773304416811546</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.626717088410196</v>
+        <v>-0.5874999999980494</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.0246237681079708</v>
+        <v>-0.001675801716540526</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>99.99999999341556</v>
+        <v>99.99999999972623</v>
       </c>
       <c r="B4" t="n">
-        <v>77.97872709047142</v>
+        <v>74.7634319133418</v>
       </c>
       <c r="C4" t="n">
-        <v>47.68229516610398</v>
+        <v>45.50754110772444</v>
       </c>
       <c r="D4" t="n">
-        <v>8.719624951249912</v>
+        <v>9.884643785585967</v>
       </c>
       <c r="E4" t="n">
-        <v>2.468335380835263</v>
+        <v>4.045260816476301</v>
       </c>
       <c r="F4" t="n">
-        <v>13.51865069906909</v>
+        <v>13.80518870123217</v>
       </c>
       <c r="G4" t="n">
-        <v>0.02645657438502493</v>
+        <v>0.02602900753417861</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.7995267641600278</v>
+        <v>-0.7710854941600738</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.9064462558629173</v>
+        <v>-0.8935900797217979</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.9465557647084614</v>
+        <v>-0.936364307328015</v>
       </c>
       <c r="K4" t="n">
-        <v>-4.942874696406419e-07</v>
+        <v>-0.0001773304416811546</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.6220069729448496</v>
+        <v>-0.5874999999980494</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.02475400367729133</v>
+        <v>-0.001675801716540526</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>57.55909872872024</v>
+        <v>82.66410364324291</v>
       </c>
       <c r="B5" t="n">
-        <v>62.19281260660543</v>
+        <v>48.66528024598473</v>
       </c>
       <c r="C5" t="n">
-        <v>47.69253028991933</v>
+        <v>45.50993270292968</v>
       </c>
       <c r="D5" t="n">
-        <v>8.256063745951991</v>
+        <v>5.000056673845238</v>
       </c>
       <c r="E5" t="n">
-        <v>2.024967529926139</v>
+        <v>4.960025953137187</v>
       </c>
       <c r="F5" t="n">
-        <v>6.933241039211455</v>
+        <v>11.75779250412397</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1908845395863809</v>
+        <v>0.04904474978683205</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.004019034740834074</v>
+        <v>-0.6063895419496654</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.6129100820744331</v>
+        <v>-0.8245718298898892</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.5528951016051517</v>
+        <v>-0.8698272621577012</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.0008702578513717618</v>
+        <v>-0.9671561111851555</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.626717088410196</v>
+        <v>-0.1423418299819978</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.0246237681079708</v>
+        <v>-0.002207267317707873</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>82.15637558491889</v>
+        <v>90.00175424175832</v>
       </c>
       <c r="B6" t="n">
-        <v>114.3442240994981</v>
+        <v>46.52682705107322</v>
       </c>
       <c r="C6" t="n">
-        <v>47.67087839829729</v>
+        <v>45.50782799126165</v>
       </c>
       <c r="D6" t="n">
-        <v>11.98563366406167</v>
+        <v>10.83171296197238</v>
       </c>
       <c r="E6" t="n">
-        <v>2.348072743217969</v>
+        <v>3.926314760366259</v>
       </c>
       <c r="F6" t="n">
-        <v>10.40019128446414</v>
+        <v>11.76113447549203</v>
       </c>
       <c r="G6" t="n">
-        <v>0.05361012554841245</v>
+        <v>0.03771896767555387</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.6455059270067484</v>
+        <v>-0.6917798005910076</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.8393589212082203</v>
+        <v>-0.8594661465422657</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.8862311534639544</v>
+        <v>-0.9057991521466303</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.008254031570880558</v>
+        <v>-0.0006645472087346761</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.4887138543785139</v>
+        <v>-0.0999239828571393</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.02489927492969036</v>
+        <v>-0.001739553613700345</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>74.63640204325495</v>
+        <v>95.14749205539154</v>
       </c>
       <c r="B7" t="n">
-        <v>87.77492058229032</v>
+        <v>52.62432966141086</v>
       </c>
       <c r="C7" t="n">
-        <v>47.68014516929038</v>
+        <v>45.50648756496701</v>
       </c>
       <c r="D7" t="n">
-        <v>13.04987873301519</v>
+        <v>10.81502273766174</v>
       </c>
       <c r="E7" t="n">
-        <v>3.394428553479073</v>
+        <v>4.72529624722526</v>
       </c>
       <c r="F7" t="n">
-        <v>9.311314602126526</v>
+        <v>12.880059301963</v>
       </c>
       <c r="G7" t="n">
-        <v>0.07638142208009094</v>
+        <v>0.03101680220351343</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.5305160193835639</v>
+        <v>-0.7356324553819323</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.7934814640080629</v>
+        <v>-0.8777154825951314</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.8348184810091086</v>
+        <v>-0.9229878689447765</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.03155516394884428</v>
+        <v>-0.01053101048875394</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.4430535746618299</v>
+        <v>-0.5529258808946647</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.02478136104629926</v>
+        <v>-0.001441681103779291</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>58.41646501065569</v>
+        <v>76.86747913805046</v>
       </c>
       <c r="B8" t="n">
-        <v>77.8417850465306</v>
+        <v>53.39773471806768</v>
       </c>
       <c r="C8" t="n">
-        <v>47.69845239455432</v>
+        <v>45.50693178433789</v>
       </c>
       <c r="D8" t="n">
-        <v>8.254373918369099</v>
+        <v>5.07870131907591</v>
       </c>
       <c r="E8" t="n">
-        <v>2.150561008422977</v>
+        <v>3.865204742551226</v>
       </c>
       <c r="F8" t="n">
-        <v>7.048368438017688</v>
+        <v>10.32124437709682</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1806278600691808</v>
+        <v>0.06362572615905825</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.04644718342715848</v>
+        <v>-0.5135158870606696</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.626403434178302</v>
+        <v>-0.7883793665020808</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.5780113684232639</v>
+        <v>-0.8276179499507121</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.0002020488323646675</v>
+        <v>-0.2283554638378236</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.6378889484499727</v>
+        <v>-0.4128509735576452</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.02454841301870788</v>
+        <v>-0.001540396519532083</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>62.89353326677047</v>
+        <v>78.83674126968768</v>
       </c>
       <c r="B9" t="n">
-        <v>58.72603049006225</v>
+        <v>45.68937827464455</v>
       </c>
       <c r="C9" t="n">
-        <v>47.6812072869018</v>
+        <v>45.53195792563509</v>
       </c>
       <c r="D9" t="n">
-        <v>7.311097613578086</v>
+        <v>5.18638354677712</v>
       </c>
       <c r="E9" t="n">
-        <v>2.055456404643624</v>
+        <v>4.191883555457761</v>
       </c>
       <c r="F9" t="n">
-        <v>7.697275679943281</v>
+        <v>10.8255211292866</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1364739948354862</v>
+        <v>0.05810710074090372</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.2334689371055831</v>
+        <v>-0.5481019432812019</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.6881044057078874</v>
+        <v>-0.8016386626073068</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.6843153804576865</v>
+        <v>-0.8436751865216963</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.001678363173580182</v>
+        <v>-0.5013031739305838</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6676169591689772</v>
+        <v>-0.3209520740812418</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.02476784626188595</v>
+        <v>-0.007101761252241573</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>79.41896947601757</v>
+        <v>71.35615025326341</v>
       </c>
       <c r="B10" t="n">
-        <v>78.75713699081135</v>
+        <v>49.33760031616052</v>
       </c>
       <c r="C10" t="n">
-        <v>47.68203033268833</v>
+        <v>45.5699333934359</v>
       </c>
       <c r="D10" t="n">
-        <v>12.21239820248314</v>
+        <v>6.502119689431392</v>
       </c>
       <c r="E10" t="n">
-        <v>2.249659183369443</v>
+        <v>4.443222202867801</v>
       </c>
       <c r="F10" t="n">
-        <v>10.15909233082381</v>
+        <v>9.3313791634971</v>
       </c>
       <c r="G10" t="n">
-        <v>0.06043863470523145</v>
+        <v>0.08362005841140532</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.6090100374782195</v>
+        <v>-0.3947429184935433</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.8245631072581384</v>
+        <v>-0.7443504524210233</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.870472880958149</v>
+        <v>-0.7696184582522263</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.0813899710220022</v>
+        <v>-0.1007621827979553</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.4848623339258034</v>
+        <v>-0.6700463215143739</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.02475737351739148</v>
+        <v>-0.01554075409686662</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>91.42874397348469</v>
+        <v>64.29081290186022</v>
       </c>
       <c r="B11" t="n">
-        <v>73.84780723048041</v>
+        <v>48.74292657129066</v>
       </c>
       <c r="C11" t="n">
-        <v>47.60829134448918</v>
+        <v>45.72445488068087</v>
       </c>
       <c r="D11" t="n">
-        <v>10.5216635138297</v>
+        <v>7.068970461208792</v>
       </c>
       <c r="E11" t="n">
-        <v>2.30011572563174</v>
+        <v>4.749979144822112</v>
       </c>
       <c r="F11" t="n">
-        <v>11.98089125288807</v>
+        <v>7.947097697511102</v>
       </c>
       <c r="G11" t="n">
-        <v>0.03637271627749259</v>
+        <v>0.1230370365571635</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.7403034810216282</v>
+        <v>-0.179796770587175</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.8798408353960102</v>
+        <v>-0.6703552127002258</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.9246980354478409</v>
+        <v>-0.6553430777231075</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.02372653364257981</v>
+        <v>-3.302666438700422e-05</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.557979092802795</v>
+        <v>-0.1381857258619288</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.02736175406312703</v>
+        <v>-0.04987886237352551</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>61.92491187831732</v>
+        <v>62.44001095472249</v>
       </c>
       <c r="B12" t="n">
-        <v>85.837034468243</v>
+        <v>51.90849611328602</v>
       </c>
       <c r="C12" t="n">
-        <v>47.68237264237946</v>
+        <v>45.50841415731859</v>
       </c>
       <c r="D12" t="n">
-        <v>7.644051205771541</v>
+        <v>7.823486781026527</v>
       </c>
       <c r="E12" t="n">
-        <v>2.120588668152536</v>
+        <v>4.994876540767811</v>
       </c>
       <c r="F12" t="n">
-        <v>7.578448185890831</v>
+        <v>7.726305127482063</v>
       </c>
       <c r="G12" t="n">
-        <v>0.1447778767116357</v>
+        <v>0.1374813741258941</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.1974527722481478</v>
+        <v>-0.1058351241032241</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.6759282849369838</v>
+        <v>-0.6459582476525244</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.6644426490093667</v>
+        <v>-0.6134296601599892</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.03201030102587326</v>
+        <v>-0.07466472014722637</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.6611852531123932</v>
+        <v>-0.2133745549643989</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.0247530178399903</v>
+        <v>-0.001869812737464172</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>69.28356695076855</v>
+        <v>81.71193122218686</v>
       </c>
       <c r="B13" t="n">
-        <v>82.89618956413837</v>
+        <v>52.66234392277083</v>
       </c>
       <c r="C13" t="n">
-        <v>47.67744803646426</v>
+        <v>45.63937629454208</v>
       </c>
       <c r="D13" t="n">
-        <v>6.427645253103083</v>
+        <v>5.141381225266134</v>
       </c>
       <c r="E13" t="n">
-        <v>2.018196646327216</v>
+        <v>4.986444666852054</v>
       </c>
       <c r="F13" t="n">
-        <v>8.82934045935651</v>
+        <v>11.54387772759609</v>
       </c>
       <c r="G13" t="n">
-        <v>0.09509429522856411</v>
+        <v>0.05112114611811618</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.4233859512948613</v>
+        <v>-0.5928752353272115</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.7548754217589722</v>
+        <v>-0.8191819593269527</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.7837120207635471</v>
+        <v>-0.8638687475606105</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.2184835370013017</v>
+        <v>-0.8507439643759275</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.7100471788988734</v>
+        <v>-0.1867765429646133</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.02481568037994767</v>
+        <v>-0.0309725098982401</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>83.44674499401937</v>
+        <v>97.94998556526966</v>
       </c>
       <c r="B14" t="n">
-        <v>83.84161512395127</v>
+        <v>52.1031515236883</v>
       </c>
       <c r="C14" t="n">
-        <v>47.71020959021246</v>
+        <v>45.57690542412379</v>
       </c>
       <c r="D14" t="n">
-        <v>11.91239488049981</v>
+        <v>10.79938454823973</v>
       </c>
       <c r="E14" t="n">
-        <v>2.209700438847988</v>
+        <v>4.041638449055418</v>
       </c>
       <c r="F14" t="n">
-        <v>10.63682828512046</v>
+        <v>13.51781157963686</v>
       </c>
       <c r="G14" t="n">
-        <v>0.05066085738868625</v>
+        <v>0.02803410238397133</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.6612333297780327</v>
+        <v>-0.7568577980495748</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.8458777468959046</v>
+        <v>-0.887127172294219</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.8928759907373639</v>
+        <v>-0.9310658304844999</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.03066465131066306</v>
+        <v>-0.09826908090765925</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.4983530038418764</v>
+        <v>-0.5728936471525463</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.02439881003414393</v>
+        <v>-0.01709009424973124</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>65.86921338440628</v>
+        <v>65.20477799332014</v>
       </c>
       <c r="B15" t="n">
-        <v>69.07339978387421</v>
+        <v>48.73665296933301</v>
       </c>
       <c r="C15" t="n">
-        <v>47.67759525078605</v>
+        <v>45.51622978889294</v>
       </c>
       <c r="D15" t="n">
-        <v>6.599033906318423</v>
+        <v>6.92931150091584</v>
       </c>
       <c r="E15" t="n">
-        <v>3.423819358525026</v>
+        <v>4.741024738293532</v>
       </c>
       <c r="F15" t="n">
-        <v>8.145656106098032</v>
+        <v>8.097779343581617</v>
       </c>
       <c r="G15" t="n">
-        <v>0.114663128747583</v>
+        <v>0.1166945478157142</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.3311803492403067</v>
+        <v>-0.2132312889412276</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.721881624541396</v>
+        <v>-0.6815603754780695</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.736634524556399</v>
+        <v>-0.6738825355770267</v>
       </c>
       <c r="K15" t="n">
-        <v>-7.505377530607944e-05</v>
+        <v>-0.02062768083017886</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.6873756595891876</v>
+        <v>-0.1010558940213696</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.0248138071694852</v>
+        <v>-0.003606619753984963</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>76.3829795865589</v>
+        <v>78.09486393671204</v>
       </c>
       <c r="B16" t="n">
-        <v>180.4590839848137</v>
+        <v>45.68937827464455</v>
       </c>
       <c r="C16" t="n">
-        <v>46.3047565797777</v>
+        <v>45.53195792563509</v>
       </c>
       <c r="D16" t="n">
-        <v>13.00110682108435</v>
+        <v>5.035354706026665</v>
       </c>
       <c r="E16" t="n">
-        <v>2.235806557441293</v>
+        <v>3.755631778920745</v>
       </c>
       <c r="F16" t="n">
-        <v>9.53798044397235</v>
+        <v>10.61169786188725</v>
       </c>
       <c r="G16" t="n">
-        <v>0.07023376042778767</v>
+        <v>0.06009592288566908</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.561115666490798</v>
+        <v>-0.5355025609436037</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.8053534171180075</v>
+        <v>-0.7967871120948682</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.848938148251868</v>
+        <v>-0.8378731592667139</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.00123110684337294</v>
+        <v>-0.3747345614060302</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.4455861836922061</v>
+        <v>-0.3555730162867708</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.04241065714798472</v>
+        <v>-0.007101761252241573</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>84.30186356686251</v>
+        <v>66.77873387416733</v>
       </c>
       <c r="B17" t="n">
-        <v>86.78933837186804</v>
+        <v>30.6200438027312</v>
       </c>
       <c r="C17" t="n">
-        <v>47.68015706345985</v>
+        <v>45.51242723420141</v>
       </c>
       <c r="D17" t="n">
-        <v>12.1653208228068</v>
+        <v>6.68936662160945</v>
       </c>
       <c r="E17" t="n">
-        <v>2.209700438847988</v>
+        <v>4.992550717466972</v>
       </c>
       <c r="F17" t="n">
-        <v>10.85591896381672</v>
+        <v>8.374829938993917</v>
       </c>
       <c r="G17" t="n">
-        <v>0.04887958603042432</v>
+        <v>0.1067572250882731</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.6710453546778032</v>
+        <v>-0.2666008148819497</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.849952960362321</v>
+        <v>-0.6997034772227473</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.8969637636446361</v>
+        <v>-0.7029340553883647</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.09138731435154529</v>
+        <v>-0.07105409980984302</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.5047407992083818</v>
+        <v>-0.03711393636195234</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.02478120970040825</v>
+        <v>-0.002761607600315213</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>68.6955583940701</v>
+        <v>93.95373669774598</v>
       </c>
       <c r="B18" t="n">
-        <v>51.75797897592239</v>
+        <v>43.67025849341333</v>
       </c>
       <c r="C18" t="n">
-        <v>47.68082278381867</v>
+        <v>45.51004348363978</v>
       </c>
       <c r="D18" t="n">
-        <v>6.059222984606637</v>
+        <v>10.68580084127484</v>
       </c>
       <c r="E18" t="n">
-        <v>2.231757486993536</v>
+        <v>4.051440290364478</v>
       </c>
       <c r="F18" t="n">
-        <v>8.625856538991647</v>
+        <v>12.58782395163124</v>
       </c>
       <c r="G18" t="n">
-        <v>0.09803050997724029</v>
+        <v>0.03240539882923274</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.4089278202094622</v>
+        <v>-0.7278074093138146</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.7496487878899493</v>
+        <v>-0.8749414109603031</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.7764980920214977</v>
+        <v>-0.9200977092209756</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.0679879593604483</v>
+        <v>-0.02814651939683565</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.7061427656363498</v>
+        <v>-0.03306445053961438</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.02477273882389509</v>
+        <v>-0.002231885253283356</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>93.97963647134382</v>
+        <v>61.0576891528252</v>
       </c>
       <c r="B19" t="n">
-        <v>76.58634131571571</v>
+        <v>53.5955963200845</v>
       </c>
       <c r="C19" t="n">
-        <v>47.19909726277286</v>
+        <v>45.52163687299542</v>
       </c>
       <c r="D19" t="n">
-        <v>10.59241992060357</v>
+        <v>7.837150285451466</v>
       </c>
       <c r="E19" t="n">
-        <v>2.238976800697765</v>
+        <v>4.791911709841171</v>
       </c>
       <c r="F19" t="n">
-        <v>12.56870993901768</v>
+        <v>7.461413336975749</v>
       </c>
       <c r="G19" t="n">
-        <v>0.03303261629335395</v>
+        <v>0.1495040250641418</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.760069791813363</v>
+        <v>-0.04478484729902604</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.8886171972196555</v>
+        <v>-0.6262505512050976</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.9321888522353504</v>
+        <v>-0.5779726589233815</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.1136816319527121</v>
+        <v>-0.0001098808541518236</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.5770344376353846</v>
+        <v>-0.2695313781664764</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.05114112350870827</v>
+        <v>-0.004808193998983995</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>59.65623662937867</v>
+        <v>61.87186845684985</v>
       </c>
       <c r="B20" t="n">
-        <v>60.57197860722955</v>
+        <v>52.06234070795631</v>
       </c>
       <c r="C20" t="n">
-        <v>47.70931497354358</v>
+        <v>45.52141769929618</v>
       </c>
       <c r="D20" t="n">
-        <v>8.003257560219341</v>
+        <v>7.663456716706827</v>
       </c>
       <c r="E20" t="n">
-        <v>2.214645640770031</v>
+        <v>4.759251286564005</v>
       </c>
       <c r="F20" t="n">
-        <v>7.224449589876793</v>
+        <v>7.583040931939493</v>
       </c>
       <c r="G20" t="n">
-        <v>0.1667454490974647</v>
+        <v>0.1421939565686981</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.1039027793704815</v>
+        <v>-0.08145696323013193</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.6449887804546852</v>
+        <v>-0.6380574827773535</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.6114792149356385</v>
+        <v>-0.5993712119557215</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.0006031079368931205</v>
+        <v>-0.002396421343283842</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.6461211088420276</v>
+        <v>-0.2364553439404747</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.02441019347349365</v>
+        <v>-0.004759488732483663</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>90.01791872123306</v>
+        <v>69.58033215756507</v>
       </c>
       <c r="B21" t="n">
-        <v>78.46486314409599</v>
+        <v>41.94243820795968</v>
       </c>
       <c r="C21" t="n">
-        <v>47.72496127063337</v>
+        <v>45.52537373609823</v>
       </c>
       <c r="D21" t="n">
-        <v>11.1138131704649</v>
+        <v>6.634551132359795</v>
       </c>
       <c r="E21" t="n">
-        <v>2.529255343509486</v>
+        <v>4.99743540590174</v>
       </c>
       <c r="F21" t="n">
-        <v>11.80340624529065</v>
+        <v>8.96407076234056</v>
       </c>
       <c r="G21" t="n">
-        <v>0.03850913365468122</v>
+        <v>0.09174089967416311</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.7282426446090497</v>
+        <v>-0.3482494494032659</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.8745039971072271</v>
+        <v>-0.7277425710095251</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.9200222792957689</v>
+        <v>-0.7458326925982393</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.08455255302854332</v>
+        <v>-0.002589634805987543</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.5474401297917149</v>
+        <v>-0.690675436997912</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.0242111040979264</v>
+        <v>-0.005638608021829306</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>85.84917714629987</v>
+        <v>75.83202005515618</v>
       </c>
       <c r="B22" t="n">
-        <v>71.4707275418294</v>
+        <v>41.00605024995704</v>
       </c>
       <c r="C22" t="n">
-        <v>47.69816398927952</v>
+        <v>45.50745155545567</v>
       </c>
       <c r="D22" t="n">
-        <v>11.18008168548037</v>
+        <v>5.07870131907591</v>
       </c>
       <c r="E22" t="n">
-        <v>2.558238907162699</v>
+        <v>4.230043173515551</v>
       </c>
       <c r="F22" t="n">
-        <v>11.13529840203247</v>
+        <v>10.07289123461871</v>
       </c>
       <c r="G22" t="n">
-        <v>0.04550320449781005</v>
+        <v>0.06681642641146382</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.6884181227462272</v>
+        <v>-0.4938596394975485</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.8574129496160815</v>
+        <v>-0.7809426970939531</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.9041512743933022</v>
+        <v>-0.8183200684650882</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.05428320769341329</v>
+        <v>-0.09620386483358624</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.5067933442727753</v>
+        <v>-0.4611723974260448</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.02455208279601941</v>
+        <v>-0.001655901212370414</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>97.70563573659587</v>
+        <v>63.19055504311735</v>
       </c>
       <c r="B23" t="n">
-        <v>61.60447870664741</v>
+        <v>51.89666526462533</v>
       </c>
       <c r="C23" t="n">
-        <v>47.68072330652241</v>
+        <v>45.51682352164031</v>
       </c>
       <c r="D23" t="n">
-        <v>9.58624858867498</v>
+        <v>8.026777224173827</v>
       </c>
       <c r="E23" t="n">
-        <v>2.537047069279994</v>
+        <v>3.861347769339837</v>
       </c>
       <c r="F23" t="n">
-        <v>13.16940760942854</v>
+        <v>7.916352687592434</v>
       </c>
       <c r="G23" t="n">
-        <v>0.02873943826145496</v>
+        <v>0.131560837049102</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.7856150397129511</v>
+        <v>-0.1367205772246172</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.900236305253253</v>
+        <v>-0.6560509260463511</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.9415871940659158</v>
+        <v>-0.6310598474330353</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.07968280080350715</v>
+        <v>-0.07640939987362885</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.6048679119605239</v>
+        <v>-0.2487071962099384</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.02477400461046946</v>
+        <v>-0.003738560364513061</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>85.88985587603351</v>
+        <v>80.71553142375234</v>
       </c>
       <c r="B24" t="n">
-        <v>68.91503313138884</v>
+        <v>50.11762766972699</v>
       </c>
       <c r="C24" t="n">
-        <v>47.68135824432285</v>
+        <v>23.79416343373958</v>
       </c>
       <c r="D24" t="n">
-        <v>11.15566239807333</v>
+        <v>5.027774615009377</v>
       </c>
       <c r="E24" t="n">
-        <v>2.14731696628665</v>
+        <v>4.66454717736281</v>
       </c>
       <c r="F24" t="n">
-        <v>11.49879216310485</v>
+        <v>11.20275007339965</v>
       </c>
       <c r="G24" t="n">
-        <v>0.04519726695436299</v>
+        <v>0.05336778541698171</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.689211510988945</v>
+        <v>-0.5781566353858154</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.8578544524683064</v>
+        <v>-0.8133884711574257</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.9045071673161297</v>
+        <v>-0.8573145548571048</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.2079088063965343</v>
+        <v>-0.4552365999706183</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.4818543016931375</v>
+        <v>-0.2332752002248906</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.02476592542281983</v>
+        <v>-0.1564110800860283</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>92.74066073820707</v>
+        <v>63.11712228811037</v>
       </c>
       <c r="B25" t="n">
-        <v>85.86289731442037</v>
+        <v>51.89666526462533</v>
       </c>
       <c r="C25" t="n">
-        <v>46.96748482082953</v>
+        <v>45.51704397221181</v>
       </c>
       <c r="D25" t="n">
-        <v>10.96563313152715</v>
+        <v>8.026777224173827</v>
       </c>
       <c r="E25" t="n">
-        <v>2.13287845714653</v>
+        <v>4.048109905369589</v>
       </c>
       <c r="F25" t="n">
-        <v>12.3657089401162</v>
+        <v>7.901791324811398</v>
       </c>
       <c r="G25" t="n">
-        <v>0.03464765196707838</v>
+        <v>0.1321330492403943</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.7506550826409605</v>
+        <v>-0.1337566649863915</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.884390317443981</v>
+        <v>-0.6550771144028931</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.9286393827826923</v>
+        <v>-0.6293761182426064</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.1299800120895086</v>
+        <v>-0.07255990650823507</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.5677792025151491</v>
+        <v>-0.2516139094289651</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.0525933278080275</v>
+        <v>-0.003787549380400851</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>68.18744672405576</v>
+        <v>61.34005299777909</v>
       </c>
       <c r="B26" t="n">
-        <v>60.37014810743479</v>
+        <v>53.84043278858834</v>
       </c>
       <c r="C26" t="n">
-        <v>47.68083000123861</v>
+        <v>45.51640621382929</v>
       </c>
       <c r="D26" t="n">
-        <v>6.059222984606637</v>
+        <v>8.078483891740694</v>
       </c>
       <c r="E26" t="n">
-        <v>2.538452768168806</v>
+        <v>4.982002491546184</v>
       </c>
       <c r="F26" t="n">
-        <v>8.517406691371979</v>
+        <v>7.564947555489177</v>
       </c>
       <c r="G26" t="n">
-        <v>0.1007488528942992</v>
+        <v>0.1470496632863873</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.3959245610364269</v>
+        <v>-0.05761533070123696</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.744951239737331</v>
+        <v>-0.6303483133449719</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.7699490511033786</v>
+        <v>-0.585477685121733</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.02238296607708927</v>
+        <v>-0.07378293274214553</v>
       </c>
       <c r="L26" t="n">
-        <v>-0.7027688726535911</v>
+        <v>-0.2580603469652248</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.02477264698672633</v>
+        <v>-0.003645825295397892</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>60.83448125159916</v>
+        <v>66.34279801326817</v>
       </c>
       <c r="B27" t="n">
-        <v>65.58851354577749</v>
+        <v>41.55684640773938</v>
       </c>
       <c r="C27" t="n">
-        <v>47.65352128107085</v>
+        <v>45.52373786870773</v>
       </c>
       <c r="D27" t="n">
-        <v>7.894002015349196</v>
+        <v>6.567041590405605</v>
       </c>
       <c r="E27" t="n">
-        <v>2.393211107384861</v>
+        <v>4.488203038546797</v>
       </c>
       <c r="F27" t="n">
-        <v>7.426639396341776</v>
+        <v>8.258954137780782</v>
       </c>
       <c r="G27" t="n">
-        <v>0.1548801673229043</v>
+        <v>0.1093391492046452</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.1541719593623528</v>
+        <v>-0.2523684618882815</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.6614927098255783</v>
+        <v>-0.6948418084864924</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.6401739757570627</v>
+        <v>-0.6952581265648738</v>
       </c>
       <c r="K27" t="n">
-        <v>-0.03396952833635885</v>
+        <v>-0.001373337094899726</v>
       </c>
       <c r="L27" t="n">
-        <v>-0.6539447261637292</v>
+        <v>-0.05482383071098107</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.02557562935102421</v>
+        <v>-0.005275081935049719</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>96.49480826294025</v>
+        <v>96.88054629298642</v>
       </c>
       <c r="B28" t="n">
-        <v>58.23680090708814</v>
+        <v>52.05591259014162</v>
       </c>
       <c r="C28" t="n">
-        <v>47.68240642790823</v>
+        <v>45.50713551306249</v>
       </c>
       <c r="D28" t="n">
-        <v>9.519802203646769</v>
+        <v>10.46072577328125</v>
       </c>
       <c r="E28" t="n">
-        <v>2.075327005740261</v>
+        <v>4.053294291907592</v>
       </c>
       <c r="F28" t="n">
-        <v>12.88058922423921</v>
+        <v>13.19960203545378</v>
       </c>
       <c r="G28" t="n">
-        <v>0.03000674130167216</v>
+        <v>0.02909447076841744</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.7778174677694484</v>
+        <v>-0.7491157729736108</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.8967045930628895</v>
+        <v>-0.8836993866114777</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.9387604418309542</v>
+        <v>-0.9281499845103048</v>
       </c>
       <c r="K28" t="n">
-        <v>-0.01723813168210194</v>
+        <v>-0.001291434210861831</v>
       </c>
       <c r="L28" t="n">
-        <v>-0.5958229463013889</v>
+        <v>-0.5652738923375282</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.02475258794020043</v>
+        <v>-0.001585669569441478</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>64.08432302525961</v>
+        <v>67.56069445757178</v>
       </c>
       <c r="B29" t="n">
-        <v>53.31014706573807</v>
+        <v>41.51444897945068</v>
       </c>
       <c r="C29" t="n">
-        <v>46.17523015946791</v>
+        <v>42.88794553288421</v>
       </c>
       <c r="D29" t="n">
-        <v>7.231736413201732</v>
+        <v>6.589737893667506</v>
       </c>
       <c r="E29" t="n">
-        <v>2.393211107384861</v>
+        <v>4.998166783475282</v>
       </c>
       <c r="F29" t="n">
-        <v>7.963660832578561</v>
+        <v>8.568787848977163</v>
       </c>
       <c r="G29" t="n">
-        <v>0.1271516577358601</v>
+        <v>0.1023018482084998</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.2747413433449452</v>
+        <v>-0.2912423238660063</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.7022247369098904</v>
+        <v>-0.7081826456574244</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.7067029694678671</v>
+        <v>-0.7161097696439455</v>
       </c>
       <c r="K29" t="n">
-        <v>-0.07537345923518882</v>
+        <v>-0.05056243180679004</v>
       </c>
       <c r="L29" t="n">
-        <v>-0.6599767267492214</v>
+        <v>-0.005346787661146268</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.0444420535253152</v>
+        <v>-0.4116299569136847</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>73.07091129588078</v>
+        <v>93.40017911483949</v>
       </c>
       <c r="B30" t="n">
-        <v>141.9167045278391</v>
+        <v>55.08857167029114</v>
       </c>
       <c r="C30" t="n">
-        <v>47.68074363034959</v>
+        <v>45.51123923133426</v>
       </c>
       <c r="D30" t="n">
-        <v>13.33634111901537</v>
+        <v>10.68612141564307</v>
       </c>
       <c r="E30" t="n">
-        <v>3.219959479772256</v>
+        <v>4.051488727605673</v>
       </c>
       <c r="F30" t="n">
-        <v>9.033975386229296</v>
+        <v>12.4657652479256</v>
       </c>
       <c r="G30" t="n">
-        <v>0.08284328323302804</v>
+        <v>0.033084034009222</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.5001129162702918</v>
+        <v>-0.7231233397268098</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.7817678136522063</v>
+        <v>-0.8729059413856604</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.8204373226875605</v>
+        <v>-0.918272162409859</v>
       </c>
       <c r="K30" t="n">
-        <v>-0.00863204094836317</v>
+        <v>-0.009760828798795296</v>
       </c>
       <c r="L30" t="n">
-        <v>-0.4208448026105161</v>
+        <v>-0.05643688181788842</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.02477374600243972</v>
+        <v>-0.002497606963169363</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>59.08907829243336</v>
+        <v>77.46867706764627</v>
       </c>
       <c r="B31" t="n">
-        <v>59.94241130721959</v>
+        <v>48.74292657129066</v>
       </c>
       <c r="C31" t="n">
-        <v>47.68066035034783</v>
+        <v>45.72820063610517</v>
       </c>
       <c r="D31" t="n">
-        <v>8.039450190244626</v>
+        <v>5.117759553042562</v>
       </c>
       <c r="E31" t="n">
-        <v>2.559529900275309</v>
+        <v>4.752682266201253</v>
       </c>
       <c r="F31" t="n">
-        <v>7.167921773275302</v>
+        <v>10.48008738758276</v>
       </c>
       <c r="G31" t="n">
-        <v>0.1727669212696394</v>
+        <v>0.06187337894029458</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.07838255248668817</v>
+        <v>-0.5244389169899998</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.6367237751629935</v>
+        <v>-0.7925397422448928</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.5967219966647177</v>
+        <v>-0.8327304667073461</v>
       </c>
       <c r="K31" t="n">
-        <v>-0.02327765616633496</v>
+        <v>-0.3189227928494918</v>
       </c>
       <c r="L31" t="n">
-        <v>-0.6345155279185798</v>
+        <v>-0.3847950701765072</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.02477480568854006</v>
+        <v>-0.05071125246781549</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>60.32863413014313</v>
+        <v>73.22914632875386</v>
       </c>
       <c r="B32" t="n">
-        <v>73.84780723048041</v>
+        <v>41.99827200551955</v>
       </c>
       <c r="C32" t="n">
-        <v>47.60829134448918</v>
+        <v>45.97095865704451</v>
       </c>
       <c r="D32" t="n">
-        <v>7.87738279426951</v>
+        <v>5.634388303903451</v>
       </c>
       <c r="E32" t="n">
-        <v>2.553550510791276</v>
+        <v>4.226783660545596</v>
       </c>
       <c r="F32" t="n">
-        <v>7.326016809985704</v>
+        <v>9.588989710800242</v>
       </c>
       <c r="G32" t="n">
-        <v>0.1598017685335265</v>
+        <v>0.07593550085731475</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.1331080716982167</v>
+        <v>-0.4392433831561174</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.6545536728545388</v>
+        <v>-0.7605969137289101</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.6282217791023402</v>
+        <v>-0.7918469114314797</v>
       </c>
       <c r="K32" t="n">
-        <v>-0.0020555816135624</v>
+        <v>-0.005577011985978641</v>
       </c>
       <c r="L32" t="n">
-        <v>-0.6505858699237592</v>
+        <v>-0.582639837991487</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.02736175406312703</v>
+        <v>-0.1046574793432219</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>63.45816209395057</v>
+        <v>81.24487528956747</v>
       </c>
       <c r="B33" t="n">
-        <v>58.72603049006225</v>
+        <v>51.9647506816671</v>
       </c>
       <c r="C33" t="n">
-        <v>47.66453756444257</v>
+        <v>25.31330378386408</v>
       </c>
       <c r="D33" t="n">
-        <v>7.30810407541071</v>
+        <v>5.010042642510625</v>
       </c>
       <c r="E33" t="n">
-        <v>2.222078633724747</v>
+        <v>3.861056422341053</v>
       </c>
       <c r="F33" t="n">
-        <v>7.812565342375454</v>
+        <v>11.33858065751457</v>
       </c>
       <c r="G33" t="n">
-        <v>0.1320025814382824</v>
+        <v>0.05213878837605222</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.2533574578744211</v>
+        <v>-0.5861048871362936</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.6948709357697073</v>
+        <v>-0.8165216965088468</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.6951466959101259</v>
+        <v>-0.860866930694173</v>
       </c>
       <c r="K33" t="n">
-        <v>-0.03537117440619977</v>
+        <v>-0.6088655438026787</v>
       </c>
       <c r="L33" t="n">
-        <v>-0.6713661295783723</v>
+        <v>-0.208572486486851</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.02514059765624766</v>
+        <v>-0.1290770540711175</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>89.05211662440567</v>
+        <v>73.59860507157177</v>
       </c>
       <c r="B34" t="n">
-        <v>78.46486314409599</v>
+        <v>30.6200438027312</v>
       </c>
       <c r="C34" t="n">
-        <v>46.17573284419148</v>
+        <v>45.51242723420141</v>
       </c>
       <c r="D34" t="n">
-        <v>11.17742349899754</v>
+        <v>5.68541626722901</v>
       </c>
       <c r="E34" t="n">
-        <v>2.529255343509486</v>
+        <v>4.992550717466972</v>
       </c>
       <c r="F34" t="n">
-        <v>11.60912629153126</v>
+        <v>9.673025260112183</v>
       </c>
       <c r="G34" t="n">
-        <v>0.04001873875716674</v>
+        <v>0.07455760007578983</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.7196258991445487</v>
+        <v>-0.4474451414243648</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.8707495425269465</v>
+        <v>-0.7636145783722349</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.9166453637006527</v>
+        <v>-0.7958768564007438</v>
       </c>
       <c r="K34" t="n">
-        <v>-0.03502811996148514</v>
+        <v>-0.05117617615518398</v>
       </c>
       <c r="L34" t="n">
-        <v>-0.5402255207830915</v>
+        <v>-0.5653984299933176</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.04443415073687184</v>
+        <v>-0.002761607600315213</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>66.4470359284919</v>
+        <v>92.24371429434426</v>
       </c>
       <c r="B35" t="n">
-        <v>64.73517111157112</v>
+        <v>31.24183239827787</v>
       </c>
       <c r="C35" t="n">
-        <v>45.50516358301783</v>
+        <v>45.77161303486564</v>
       </c>
       <c r="D35" t="n">
-        <v>6.799309850247163</v>
+        <v>10.69246348903074</v>
       </c>
       <c r="E35" t="n">
-        <v>2.493539544552459</v>
+        <v>4.522660364099517</v>
       </c>
       <c r="F35" t="n">
-        <v>8.310868216670288</v>
+        <v>12.22666583450573</v>
       </c>
       <c r="G35" t="n">
-        <v>0.1110795524489705</v>
+        <v>0.0345723954279031</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.3480277582080991</v>
+        <v>-0.7129683058883272</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.7277988620744509</v>
+        <v>-0.8685164567482319</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.7453963455837275</v>
+        <v>-0.9142792031209646</v>
       </c>
       <c r="K35" t="n">
-        <v>-0.05638076317479561</v>
+        <v>-0.05657437170570197</v>
       </c>
       <c r="L35" t="n">
-        <v>-0.6912124370966107</v>
+        <v>-0.002772380578415594</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.05187721541692415</v>
+        <v>-0.06035845219236474</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>98.29948192374547</v>
+        <v>64.54534493564853</v>
       </c>
       <c r="B36" t="n">
-        <v>61.60447870664741</v>
+        <v>48.31416916343398</v>
       </c>
       <c r="C36" t="n">
-        <v>47.68071549376714</v>
+        <v>45.72647591039378</v>
       </c>
       <c r="D36" t="n">
-        <v>9.58624858867498</v>
+        <v>7.06934420543312</v>
       </c>
       <c r="E36" t="n">
-        <v>2.557360009379961</v>
+        <v>4.15973535523119</v>
       </c>
       <c r="F36" t="n">
-        <v>13.30552781991596</v>
+        <v>7.998749905093995</v>
       </c>
       <c r="G36" t="n">
-        <v>0.02814166561214806</v>
+        <v>0.1212429643750856</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.7893067026030534</v>
+        <v>-0.1892847271854639</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.9018887439729658</v>
+        <v>-0.6735201240634723</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.9429142078232443</v>
+        <v>-0.6606285166268199</v>
       </c>
       <c r="K36" t="n">
-        <v>-0.1036751092016581</v>
+        <v>-0.01775971384080751</v>
       </c>
       <c r="L36" t="n">
-        <v>-0.6093039843873908</v>
+        <v>-0.1278453619892789</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.02477410402290956</v>
+        <v>-0.05032798008750727</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>58.83187724751627</v>
+        <v>70.33676557718292</v>
       </c>
       <c r="B37" t="n">
-        <v>59.94241130721959</v>
+        <v>52.21696556514966</v>
       </c>
       <c r="C37" t="n">
-        <v>47.69789209250422</v>
+        <v>45.53195792563509</v>
       </c>
       <c r="D37" t="n">
-        <v>8.039450190244626</v>
+        <v>6.5059666907166</v>
       </c>
       <c r="E37" t="n">
-        <v>2.559529900275309</v>
+        <v>4.191883555457761</v>
       </c>
       <c r="F37" t="n">
-        <v>7.120873749216883</v>
+        <v>9.10417107271299</v>
       </c>
       <c r="G37" t="n">
-        <v>0.1756321949058054</v>
+        <v>0.08814413504683524</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.06644042793510775</v>
+        <v>-0.3686536015389239</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.6328700359335493</v>
+        <v>-0.7349988704714632</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.5897629438810871</v>
+        <v>-0.7563457330564961</v>
       </c>
       <c r="K37" t="n">
-        <v>-0.01066244418180618</v>
+        <v>-0.02180209178557505</v>
       </c>
       <c r="L37" t="n">
-        <v>-0.633204551721348</v>
+        <v>-0.695466181988825</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.02455554251296719</v>
+        <v>-0.007101761252241573</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>94.89519064274232</v>
+        <v>96.25881352117305</v>
       </c>
       <c r="B38" t="n">
-        <v>61.60447870664741</v>
+        <v>46.52682705107322</v>
       </c>
       <c r="C38" t="n">
-        <v>47.68071608910246</v>
+        <v>45.50710587212693</v>
       </c>
       <c r="D38" t="n">
-        <v>10.93930727767366</v>
+        <v>10.83171296197238</v>
       </c>
       <c r="E38" t="n">
-        <v>2.377178793174801</v>
+        <v>3.926314760366259</v>
       </c>
       <c r="F38" t="n">
-        <v>12.81943879844686</v>
+        <v>13.13410495269264</v>
       </c>
       <c r="G38" t="n">
-        <v>0.03195096816744163</v>
+        <v>0.02978626058402521</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.7666296223462779</v>
+        <v>-0.7443396331131732</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.8915519697993238</v>
+        <v>-0.8815551922666576</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.9346294564747869</v>
+        <v>-0.9263281976922114</v>
       </c>
       <c r="K38" t="n">
-        <v>-0.2057260620856478</v>
+        <v>-0.04875545105470659</v>
       </c>
       <c r="L38" t="n">
-        <v>-0.5838736911372693</v>
+        <v>-0.5608440463383579</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.02477409644763859</v>
+        <v>-0.001579082694873751</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>57.55909872872024</v>
+        <v>67.39406681282713</v>
       </c>
       <c r="B39" t="n">
-        <v>60.52992490619051</v>
+        <v>41.08255794767197</v>
       </c>
       <c r="C39" t="n">
-        <v>47.69253028991933</v>
+        <v>45.50893262506256</v>
       </c>
       <c r="D39" t="n">
-        <v>8.180795915342189</v>
+        <v>6.567041590405605</v>
       </c>
       <c r="E39" t="n">
-        <v>2.013007796115916</v>
+        <v>4.488203038546797</v>
       </c>
       <c r="F39" t="n">
-        <v>6.957149589951446</v>
+        <v>8.479360203686342</v>
       </c>
       <c r="G39" t="n">
-        <v>0.1907253003892195</v>
+        <v>0.1031669087344451</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.00418983243738017</v>
+        <v>-0.2861385098842745</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.6129916560218051</v>
+        <v>-0.7064308404508194</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.5530214819203588</v>
+        <v>-0.7133987562241491</v>
       </c>
       <c r="K39" t="n">
-        <v>-0.02412739452573357</v>
+        <v>-0.08556191279055761</v>
       </c>
       <c r="L39" t="n">
-        <v>-0.6213714143791713</v>
+        <v>-0.01211603572889797</v>
       </c>
       <c r="M39" t="n">
-        <v>-0.0246237681079708</v>
+        <v>-0.001985027791678445</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>73.64020766482591</v>
+        <v>72.09061060517787</v>
       </c>
       <c r="B40" t="n">
-        <v>135.5749003558577</v>
+        <v>41.08255794767197</v>
       </c>
       <c r="C40" t="n">
-        <v>47.66871419605169</v>
+        <v>45.52373786870773</v>
       </c>
       <c r="D40" t="n">
-        <v>13.34094710852616</v>
+        <v>6.567041590405605</v>
       </c>
       <c r="E40" t="n">
-        <v>3.470710031437124</v>
+        <v>4.488203038546797</v>
       </c>
       <c r="F40" t="n">
-        <v>9.141420325933847</v>
+        <v>9.508819950523177</v>
       </c>
       <c r="G40" t="n">
-        <v>0.08051413104971701</v>
+        <v>0.0805592579128903</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.5113300315808679</v>
+        <v>-0.4126218105318326</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.7860360078504731</v>
+        <v>-0.7508134214586722</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.825764739515107</v>
+        <v>-0.7786043070495008</v>
       </c>
       <c r="K40" t="n">
-        <v>-0.02096677259938505</v>
+        <v>-0.1736125187375107</v>
       </c>
       <c r="L40" t="n">
-        <v>-0.425097486183538</v>
+        <v>-0.635771505091699</v>
       </c>
       <c r="M40" t="n">
-        <v>-0.02497566298036262</v>
+        <v>-0.005275081935049719</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>85.84917714629987</v>
+        <v>75.61447834707593</v>
       </c>
       <c r="B41" t="n">
-        <v>80.52679444144792</v>
+        <v>44.50727298248769</v>
       </c>
       <c r="C41" t="n">
-        <v>47.67717670218987</v>
+        <v>45.50745155545567</v>
       </c>
       <c r="D41" t="n">
-        <v>11.46154738109108</v>
+        <v>5.07870131907591</v>
       </c>
       <c r="E41" t="n">
-        <v>2.584941121798898</v>
+        <v>4.228155543229941</v>
       </c>
       <c r="F41" t="n">
-        <v>11.01643696538628</v>
+        <v>10.02113988887795</v>
       </c>
       <c r="G41" t="n">
-        <v>0.04566165859312189</v>
+        <v>0.06751362439183384</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.6881645666826803</v>
+        <v>-0.4895931363339541</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.8572322852993414</v>
+        <v>-0.779337914744643</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.9040255171748007</v>
+        <v>-0.8162859814292815</v>
       </c>
       <c r="K41" t="n">
-        <v>-0.02033702248346787</v>
+        <v>-0.0684375029390791</v>
       </c>
       <c r="L41" t="n">
-        <v>-0.5162993395408624</v>
+        <v>-0.471324343803123</v>
       </c>
       <c r="M41" t="n">
-        <v>-0.02481913293942126</v>
+        <v>-0.001655901212370414</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>64.96451820871397</v>
+        <v>69.15592435741992</v>
       </c>
       <c r="B42" t="n">
-        <v>73.91875957531124</v>
+        <v>37.79509389097325</v>
       </c>
       <c r="C42" t="n">
-        <v>47.67745680377585</v>
+        <v>45.51646789803468</v>
       </c>
       <c r="D42" t="n">
-        <v>6.862337891273999</v>
+        <v>6.351664520717422</v>
       </c>
       <c r="E42" t="n">
-        <v>2.036411780993943</v>
+        <v>4.993137661519094</v>
       </c>
       <c r="F42" t="n">
-        <v>8.016167044990357</v>
+        <v>8.813373212150028</v>
       </c>
       <c r="G42" t="n">
-        <v>0.12079460668971</v>
+        <v>0.09376010755545071</v>
       </c>
       <c r="H42" t="n">
-        <v>-0.303333655616693</v>
+        <v>-0.3382918366769436</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.7121301197704148</v>
+        <v>-0.7246185626009211</v>
       </c>
       <c r="J42" t="n">
-        <v>-0.7219645416722879</v>
+        <v>-0.7408626878973199</v>
       </c>
       <c r="K42" t="n">
-        <v>-0.01191045370714706</v>
+        <v>-0.02556985729705721</v>
       </c>
       <c r="L42" t="n">
-        <v>-0.6813684275476213</v>
+        <v>-0.01257799418546146</v>
       </c>
       <c r="M42" t="n">
-        <v>-0.0248155688213733</v>
+        <v>-0.003659532896597151</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>60.03541579427549</v>
+        <v>90.94089645934262</v>
       </c>
       <c r="B43" t="n">
-        <v>76.74666259763025</v>
+        <v>46.52682705107322</v>
       </c>
       <c r="C43" t="n">
-        <v>48.16524145114634</v>
+        <v>45.50782799126165</v>
       </c>
       <c r="D43" t="n">
-        <v>7.889818789462967</v>
+        <v>10.83171296197238</v>
       </c>
       <c r="E43" t="n">
-        <v>2.590661766385387</v>
+        <v>4.967092866420233</v>
       </c>
       <c r="F43" t="n">
-        <v>7.287253723863039</v>
+        <v>11.96132957970987</v>
       </c>
       <c r="G43" t="n">
-        <v>0.1627979815303234</v>
+        <v>0.03635967540401718</v>
       </c>
       <c r="H43" t="n">
-        <v>-0.1205154952606364</v>
+        <v>-0.700905161068532</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.6504162283419562</v>
+        <v>-0.8633456231061069</v>
       </c>
       <c r="J43" t="n">
-        <v>-0.6210232005639011</v>
+        <v>-0.9094753589610413</v>
       </c>
       <c r="K43" t="n">
-        <v>-0.001258792669638995</v>
+        <v>-0.03194937460925565</v>
       </c>
       <c r="L43" t="n">
-        <v>-0.6486388819992895</v>
+        <v>-0.05922782009515293</v>
       </c>
       <c r="M43" t="n">
-        <v>-0.004453471010993309</v>
+        <v>-0.001739553613700345</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>77.87074420690475</v>
+        <v>99.21613163393833</v>
       </c>
       <c r="B44" t="n">
-        <v>181.1968785634131</v>
+        <v>54.31680724392184</v>
       </c>
       <c r="C44" t="n">
-        <v>46.20562040770113</v>
+        <v>45.50754160191573</v>
       </c>
       <c r="D44" t="n">
-        <v>12.82390372977802</v>
+        <v>10.0338713417038</v>
       </c>
       <c r="E44" t="n">
-        <v>3.741347220120057</v>
+        <v>4.233652428945598</v>
       </c>
       <c r="F44" t="n">
-        <v>9.772126607178018</v>
+        <v>13.65177737864457</v>
       </c>
       <c r="G44" t="n">
-        <v>0.06538652582833392</v>
+        <v>0.02675636330024302</v>
       </c>
       <c r="H44" t="n">
-        <v>-0.5852431043976493</v>
+        <v>-0.7658218545123628</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.8148958129276535</v>
+        <v>-0.8912032082954218</v>
       </c>
       <c r="J44" t="n">
-        <v>-0.8598636698481135</v>
+        <v>-0.9344189467503005</v>
       </c>
       <c r="K44" t="n">
-        <v>-0.006040971370984819</v>
+        <v>-0.0007581282181715271</v>
       </c>
       <c r="L44" t="n">
-        <v>-0.456699889147928</v>
+        <v>-0.5819149378918106</v>
       </c>
       <c r="M44" t="n">
-        <v>-0.04396428348124094</v>
+        <v>-0.001675911536829638</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>61.27135563172919</v>
+        <v>62.15509596016514</v>
       </c>
       <c r="B45" t="n">
-        <v>66.36428878134028</v>
+        <v>51.92386852720412</v>
       </c>
       <c r="C45" t="n">
-        <v>47.66872555991667</v>
+        <v>45.51755052269353</v>
       </c>
       <c r="D45" t="n">
-        <v>8.196133773193694</v>
+        <v>8.026777224173827</v>
       </c>
       <c r="E45" t="n">
-        <v>2.530882563833154</v>
+        <v>4.22618620030414</v>
       </c>
       <c r="F45" t="n">
-        <v>7.57374979342339</v>
+        <v>7.712504831985608</v>
       </c>
       <c r="G45" t="n">
-        <v>0.1509224730369389</v>
+        <v>0.1399380078076853</v>
       </c>
       <c r="H45" t="n">
-        <v>-0.1716519505284607</v>
+        <v>-0.09362460618123745</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.6672556116019953</v>
+        <v>-0.6419763961287706</v>
       </c>
       <c r="J45" t="n">
-        <v>-0.6499997681196139</v>
+        <v>-0.6063920422503182</v>
       </c>
       <c r="K45" t="n">
-        <v>-0.1255218335813798</v>
+        <v>-0.1057223257786228</v>
       </c>
       <c r="L45" t="n">
-        <v>-0.6568455991262141</v>
+        <v>-0.2249492266182912</v>
       </c>
       <c r="M45" t="n">
-        <v>-0.02497521422271174</v>
+        <v>-0.003900116154118421</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>78.61041592040256</v>
+        <v>60.54172384551233</v>
       </c>
       <c r="B46" t="n">
-        <v>142.290071677531</v>
+        <v>53.96933851184451</v>
       </c>
       <c r="C46" t="n">
-        <v>47.68235917630994</v>
+        <v>45.52344035060979</v>
       </c>
       <c r="D46" t="n">
-        <v>13.01865444701044</v>
+        <v>8.081938298500711</v>
       </c>
       <c r="E46" t="n">
-        <v>3.584800448030062</v>
+        <v>4.926798101994704</v>
       </c>
       <c r="F46" t="n">
-        <v>9.950229574294216</v>
+        <v>7.413069651194516</v>
       </c>
       <c r="G46" t="n">
-        <v>0.06322040895652013</v>
+        <v>0.1544563460945706</v>
       </c>
       <c r="H46" t="n">
-        <v>-0.5964490609344443</v>
+        <v>-0.02046270531022507</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.8193401933734711</v>
+        <v>-0.6184769778341266</v>
       </c>
       <c r="J46" t="n">
-        <v>-0.8648574320059101</v>
+        <v>-0.5636222061408022</v>
       </c>
       <c r="K46" t="n">
-        <v>-0.08147006624757269</v>
+        <v>-0.03233175422636902</v>
       </c>
       <c r="L46" t="n">
-        <v>-0.462225288425021</v>
+        <v>-0.2904924687760615</v>
       </c>
       <c r="M46" t="n">
-        <v>-0.02475318918732854</v>
+        <v>-0.005208966802175002</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>70.4739416168249</v>
+        <v>74.51195795971263</v>
       </c>
       <c r="B47" t="n">
-        <v>82.47187284781189</v>
+        <v>37.95509192193391</v>
       </c>
       <c r="C47" t="n">
-        <v>47.6812072869018</v>
+        <v>45.9550397644337</v>
       </c>
       <c r="D47" t="n">
-        <v>6.014122863524759</v>
+        <v>5.661168137514491</v>
       </c>
       <c r="E47" t="n">
-        <v>2.201371705950901</v>
+        <v>4.575247670807197</v>
       </c>
       <c r="F47" t="n">
-        <v>8.934037557202576</v>
+        <v>9.891827712692436</v>
       </c>
       <c r="G47" t="n">
-        <v>0.089292679298151</v>
+        <v>0.07129729641780121</v>
       </c>
       <c r="H47" t="n">
-        <v>-0.4514868523634655</v>
+        <v>-0.4670206980597357</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.7651908475400737</v>
+        <v>-0.7708593256710465</v>
       </c>
       <c r="J47" t="n">
-        <v>-0.7975922349027409</v>
+        <v>-0.8054141541790683</v>
       </c>
       <c r="K47" t="n">
-        <v>-0.06823207902694092</v>
+        <v>-0.1451278969708731</v>
       </c>
       <c r="L47" t="n">
-        <v>-0.7073808897579423</v>
+        <v>-0.5227752952134102</v>
       </c>
       <c r="M47" t="n">
-        <v>-0.02476784626188595</v>
+        <v>-0.1011199476519326</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>67.35970266349233</v>
+        <v>80.02990389866143</v>
       </c>
       <c r="B48" t="n">
-        <v>78.77991856370573</v>
+        <v>59.10047839165416</v>
       </c>
       <c r="C48" t="n">
-        <v>47.69002388708862</v>
+        <v>20.43846800526665</v>
       </c>
       <c r="D48" t="n">
-        <v>6.457833475692325</v>
+        <v>5.097387010129286</v>
       </c>
       <c r="E48" t="n">
-        <v>2.374468528193259</v>
+        <v>4.630670675298965</v>
       </c>
       <c r="F48" t="n">
-        <v>8.426106012711237</v>
+        <v>10.99825859748198</v>
       </c>
       <c r="G48" t="n">
-        <v>0.105507952616822</v>
+        <v>0.05500346582074735</v>
       </c>
       <c r="H48" t="n">
-        <v>-0.3737486904212283</v>
+        <v>-0.5675779897029984</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.7369661277496607</v>
+        <v>-0.8092474965639649</v>
       </c>
       <c r="J48" t="n">
-        <v>-0.7586573334370473</v>
+        <v>-0.8525549529925233</v>
       </c>
       <c r="K48" t="n">
-        <v>-0.07396560926959611</v>
+        <v>-0.1902133540288846</v>
       </c>
       <c r="L48" t="n">
-        <v>-0.6972726007860776</v>
+        <v>-0.2652711513957999</v>
       </c>
       <c r="M48" t="n">
-        <v>-0.02465566052133969</v>
+        <v>-0.03967747479297942</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>63.70400607203493</v>
+        <v>70.73616655685687</v>
       </c>
       <c r="B49" t="n">
-        <v>71.55700544028147</v>
+        <v>30.6200438027312</v>
       </c>
       <c r="C49" t="n">
-        <v>47.6812072869018</v>
+        <v>45.76582855714221</v>
       </c>
       <c r="D49" t="n">
-        <v>7.511145062065844</v>
+        <v>6.37631653091975</v>
       </c>
       <c r="E49" t="n">
-        <v>2.546931086942915</v>
+        <v>4.916475687242971</v>
       </c>
       <c r="F49" t="n">
-        <v>7.89911139861975</v>
+        <v>9.172823103129861</v>
       </c>
       <c r="G49" t="n">
-        <v>0.1301839097729436</v>
+        <v>0.08631380512239996</v>
       </c>
       <c r="H49" t="n">
-        <v>-0.2617158992505194</v>
+        <v>-0.3790888786636261</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.6977121609766097</v>
+        <v>-0.7387350170019149</v>
       </c>
       <c r="J49" t="n">
-        <v>-0.6996609599490434</v>
+        <v>-0.7616803822369603</v>
       </c>
       <c r="K49" t="n">
-        <v>-0.1014433867685278</v>
+        <v>-0.01901444616111426</v>
       </c>
       <c r="L49" t="n">
-        <v>-0.6729985488307957</v>
+        <v>-0.6979957215267603</v>
       </c>
       <c r="M49" t="n">
-        <v>-0.02476784626188595</v>
+        <v>-0.05907301269826984</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>70.4739416168249</v>
+        <v>68.36740507061209</v>
       </c>
       <c r="B50" t="n">
-        <v>82.47187284781189</v>
+        <v>41.08255794767197</v>
       </c>
       <c r="C50" t="n">
-        <v>47.6812072869018</v>
+        <v>45.50848868870222</v>
       </c>
       <c r="D50" t="n">
-        <v>6.014122863524759</v>
+        <v>6.567041590405605</v>
       </c>
       <c r="E50" t="n">
-        <v>2.031919385500054</v>
+        <v>4.361911953731081</v>
       </c>
       <c r="F50" t="n">
-        <v>8.934037557202576</v>
+        <v>8.686914992893694</v>
       </c>
       <c r="G50" t="n">
-        <v>0.089292679298151</v>
+        <v>0.09785401887385388</v>
       </c>
       <c r="H50" t="n">
-        <v>-0.4514868523634655</v>
+        <v>-0.3155880947108437</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.7651908475400737</v>
+        <v>-0.7166526161930301</v>
       </c>
       <c r="J50" t="n">
-        <v>-0.7975922349027409</v>
+        <v>-0.7289890507122457</v>
       </c>
       <c r="K50" t="n">
-        <v>-0.06823207902694092</v>
+        <v>-0.02639802922509675</v>
       </c>
       <c r="L50" t="n">
-        <v>-0.7073808897579423</v>
+        <v>-0.04379021595493804</v>
       </c>
       <c r="M50" t="n">
-        <v>-0.02476784626188595</v>
+        <v>-0.001886375267158569</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>77.34716900558593</v>
+        <v>74.27256950070576</v>
       </c>
       <c r="B51" t="n">
-        <v>87.77492058229032</v>
+        <v>37.95509192193391</v>
       </c>
       <c r="C51" t="n">
-        <v>47.68014516929038</v>
+        <v>46.27346879720883</v>
       </c>
       <c r="D51" t="n">
-        <v>13.04987873301519</v>
+        <v>5.634388303903451</v>
       </c>
       <c r="E51" t="n">
-        <v>3.394428553479073</v>
+        <v>4.050056113618684</v>
       </c>
       <c r="F51" t="n">
-        <v>9.726237792355869</v>
+        <v>9.838415870888509</v>
       </c>
       <c r="G51" t="n">
-        <v>0.06709252483649078</v>
+        <v>0.07213647426524938</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.5768857559751727</v>
+        <v>-0.4619764663252296</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.8115555135862114</v>
+        <v>-0.7689849205316359</v>
       </c>
       <c r="J51" t="n">
-        <v>-0.8560960291321891</v>
+        <v>-0.8029668713168054</v>
       </c>
       <c r="K51" t="n">
-        <v>-0.05819898275496008</v>
+        <v>-0.1184748078522082</v>
       </c>
       <c r="L51" t="n">
-        <v>-0.4527887458852087</v>
+        <v>-0.5339467566337314</v>
       </c>
       <c r="M51" t="n">
-        <v>-0.02478136104629926</v>
+        <v>-0.1718819549352955</v>
       </c>
     </row>
   </sheetData>
